--- a/BWI/bestwine_output/bestwine_Uganda.xlsx
+++ b/BWI/bestwine_output/bestwine_Uganda.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1187,6 +1187,71 @@
       <c r="Z7" s="4" t="inlineStr"/>
       <c r="AA7" s="4" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>43708</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Kampala</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Central Region</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Ggaba Road</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>info@supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uganda.xlsx
+++ b/BWI/bestwine_output/bestwine_Uganda.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1252,6 +1252,71 @@
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>43708</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Kampala</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Central Region</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Ggaba Road</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>info@supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uganda.xlsx
+++ b/BWI/bestwine_output/bestwine_Uganda.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1317,6 +1317,71 @@
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>43708</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Kampala</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Central Region</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Ggaba Road</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>info@supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uganda.xlsx
+++ b/BWI/bestwine_output/bestwine_Uganda.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1382,6 +1382,71 @@
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>43708</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Kampala</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Central Region</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Ggaba Road</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>info@supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uganda.xlsx
+++ b/BWI/bestwine_output/bestwine_Uganda.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1447,6 +1447,71 @@
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Online Supermarket Uganda</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>43708</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Kampala</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Central Region</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Ggaba Road</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>info@supermarket.co.ug</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
